--- a/artfynd/A 24409-2021 artfynd.xlsx
+++ b/artfynd/A 24409-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 24409-2021 artfynd.xlsx
+++ b/artfynd/A 24409-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1293,10 +1293,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>66544522</v>
+        <v>120486082</v>
       </c>
       <c r="B7" t="n">
-        <v>89412</v>
+        <v>56532</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1305,41 +1305,57 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nabbnäs E, Ly lm</t>
+          <t>Börtingtjärnen, Nabbnäs, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557343.9500621258</v>
+        <v>557511</v>
       </c>
       <c r="R7" t="n">
-        <v>7313805.357225817</v>
+        <v>7314093</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1363,22 +1379,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,31 +1405,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>25250</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Bernt-Erik Nordenström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Bernt-Erik Nordenström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>66544521</v>
+        <v>120486185</v>
       </c>
       <c r="B8" t="n">
-        <v>77177</v>
+        <v>56524</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1426,37 +1437,53 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nabbnäs E, Ly lm</t>
+          <t>Börtingtjärnen, Nabbnäs, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557552.5743103321</v>
+        <v>557511</v>
       </c>
       <c r="R8" t="n">
-        <v>7313818.131272775</v>
+        <v>7314093</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1480,22 +1507,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>vid  sista  på kartan markerade huset före sjöforsen,   mellan Ammarnäsvgn och Gautsträsk</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,31 +1538,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>25249</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Bernt-Erik Nordenström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Bernt-Erik Nordenström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>66544520</v>
+        <v>66544522</v>
       </c>
       <c r="B9" t="n">
-        <v>89317</v>
+        <v>89412</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1543,21 +1570,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3242</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1567,10 +1594,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557585.4108167831</v>
+        <v>557343.9500621258</v>
       </c>
       <c r="R9" t="n">
-        <v>7313811.444012655</v>
+        <v>7313805.357225817</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1626,7 +1653,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>25248</t>
+          <t>25250</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1644,10 +1671,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>93819789</v>
+        <v>66544521</v>
       </c>
       <c r="B10" t="n">
-        <v>57193</v>
+        <v>77177</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1660,45 +1687,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>206004</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gautsträsk, Ammarnäs, Ammarnäs, Ly lm</t>
+          <t>Nabbnäs E, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557932.0448319349</v>
+        <v>557552.5743103321</v>
       </c>
       <c r="R10" t="n">
-        <v>7313851.940869053</v>
+        <v>7313818.131272775</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1722,7 +1741,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-05-21</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1732,7 +1751,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-05-21</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1748,23 +1767,28 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>25249</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Rolf Segerstedt</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Rolf Segerstedt</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>95181786</v>
+        <v>66544520</v>
       </c>
       <c r="B11" t="n">
         <v>89317</v>
@@ -1798,20 +1822,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Nabbnäs E, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557659.3462767266</v>
+        <v>557585.4108167831</v>
       </c>
       <c r="R11" t="n">
-        <v>7313753.322394</v>
+        <v>7313811.444012655</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1835,7 +1858,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1845,7 +1868,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1861,26 +1884,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>25248</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>106068564</v>
+        <v>93819789</v>
       </c>
       <c r="B12" t="n">
-        <v>56395</v>
+        <v>57193</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1893,45 +1921,45 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nabbnäs, Ly lm</t>
+          <t>Gautsträsk, Ammarnäs, Ammarnäs, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557341.094957336</v>
+        <v>557932.0448319349</v>
       </c>
       <c r="R12" t="n">
-        <v>7314415.254025667</v>
+        <v>7313851.940869053</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1955,7 +1983,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-01-04</t>
+          <t>2021-05-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -1965,7 +1993,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-01-04</t>
+          <t>2021-05-21</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -1985,22 +2013,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Rolf Segerstedt</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Rolf Segerstedt</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>106068609</v>
+        <v>95181786</v>
       </c>
       <c r="B13" t="n">
-        <v>56540</v>
+        <v>89317</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2013,49 +2041,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>3242</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nabbnäs, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557178.5243778926</v>
+        <v>557659.3462767266</v>
       </c>
       <c r="R13" t="n">
-        <v>7314676.100958445</v>
+        <v>7313753.322394</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2079,7 +2096,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-01-04</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -2089,7 +2106,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-01-04</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2121,7 +2138,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>106181512</v>
+        <v>106068564</v>
       </c>
       <c r="B14" t="n">
         <v>56395</v>
@@ -2165,14 +2182,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Börtingtjärn, Ly lm</t>
+          <t>Nabbnäs, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557563.1252945462</v>
+        <v>557341.094957336</v>
       </c>
       <c r="R14" t="n">
-        <v>7313923.278383149</v>
+        <v>7314415.254025667</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2199,7 +2216,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-01-24</t>
+          <t>2023-01-04</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2209,17 +2226,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-01-24</t>
+          <t>2023-01-04</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rinhack. Tämligen färskt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2246,10 +2258,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>106181822</v>
+        <v>106068609</v>
       </c>
       <c r="B15" t="n">
-        <v>56395</v>
+        <v>56540</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2262,45 +2274,49 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Börtingtjärn, Nabbnäs, Ly lm</t>
+          <t>Nabbnäs, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557150.1442167946</v>
+        <v>557178.5243778926</v>
       </c>
       <c r="R15" t="n">
-        <v>7314562.870367996</v>
+        <v>7314676.100958445</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2324,7 +2340,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-01-24</t>
+          <t>2023-01-04</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -2334,7 +2350,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-01-24</t>
+          <t>2023-01-04</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2366,10 +2382,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>66544516</v>
+        <v>106181512</v>
       </c>
       <c r="B16" t="n">
-        <v>78570</v>
+        <v>56395</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2382,37 +2398,45 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nabbnäs E, Ly lm</t>
+          <t>Börtingtjärn, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>557811.1036065554</v>
+        <v>557563.1252945462</v>
       </c>
       <c r="R16" t="n">
-        <v>7313445.641976926</v>
+        <v>7313923.278383149</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2436,7 +2460,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2023-01-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -2446,7 +2470,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2023-01-24</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2454,6 +2478,11 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rinhack. Tämligen färskt</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2462,31 +2491,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>25244</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>66544518</v>
+        <v>106181822</v>
       </c>
       <c r="B17" t="n">
-        <v>78602</v>
+        <v>56395</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2495,41 +2519,49 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nabbnäs E, Ly lm</t>
+          <t>Börtingtjärn, Nabbnäs, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>557811.1036065554</v>
+        <v>557150.1442167946</v>
       </c>
       <c r="R17" t="n">
-        <v>7313445.641976926</v>
+        <v>7314562.870367996</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2553,7 +2585,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2023-01-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -2563,7 +2595,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2023-01-24</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2579,31 +2611,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>25246</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>66544517</v>
+        <v>66544516</v>
       </c>
       <c r="B18" t="n">
-        <v>78503</v>
+        <v>78570</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2612,25 +2639,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2699,7 +2726,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>25245</t>
+          <t>25244</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2717,10 +2744,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>95133646</v>
+        <v>66544518</v>
       </c>
       <c r="B19" t="n">
-        <v>56411</v>
+        <v>78602</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2729,44 +2756,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Nabbnäs E, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>557549.2252521986</v>
+        <v>557811.1036065554</v>
       </c>
       <c r="R19" t="n">
-        <v>7313517.938556333</v>
+        <v>7313445.641976926</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2790,7 +2814,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -2800,7 +2824,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -2816,26 +2840,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>25246</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>95133123</v>
+        <v>66544517</v>
       </c>
       <c r="B20" t="n">
-        <v>78072</v>
+        <v>78503</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2844,42 +2873,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Nabbnäs E, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>557451.3615532392</v>
+        <v>557811.1036065554</v>
       </c>
       <c r="R20" t="n">
-        <v>7313525.767571403</v>
+        <v>7313445.641976926</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2903,7 +2931,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -2913,7 +2941,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -2929,26 +2957,31 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>25245</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>95133125</v>
+        <v>95133646</v>
       </c>
       <c r="B21" t="n">
-        <v>78098</v>
+        <v>56411</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2961,35 +2994,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>557451.3615532392</v>
+        <v>557549.2252521986</v>
       </c>
       <c r="R21" t="n">
-        <v>7313525.767571403</v>
+        <v>7313517.938556333</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3058,10 +3093,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>95133810</v>
+        <v>95133123</v>
       </c>
       <c r="B22" t="n">
-        <v>89317</v>
+        <v>78072</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3074,21 +3109,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3242</v>
+        <v>229821</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3099,10 +3134,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>557561.2011936309</v>
+        <v>557451.3615532392</v>
       </c>
       <c r="R22" t="n">
-        <v>7313613.325183534</v>
+        <v>7313525.767571403</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3171,10 +3206,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>95132995</v>
+        <v>95133125</v>
       </c>
       <c r="B23" t="n">
-        <v>78503</v>
+        <v>78098</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3183,25 +3218,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3212,10 +3247,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>557469.5464570362</v>
+        <v>557451.3615532392</v>
       </c>
       <c r="R23" t="n">
-        <v>7313597.186250712</v>
+        <v>7313525.767571403</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3284,10 +3319,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>95133000</v>
+        <v>95133810</v>
       </c>
       <c r="B24" t="n">
-        <v>78437</v>
+        <v>89317</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3300,21 +3335,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2080</v>
+        <v>3242</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skorpgelélav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rostania occultata</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3325,10 +3360,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>557469.5464570362</v>
+        <v>557561.2011936309</v>
       </c>
       <c r="R24" t="n">
-        <v>7313597.186250712</v>
+        <v>7313613.325183534</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3397,10 +3432,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>95133592</v>
+        <v>95132995</v>
       </c>
       <c r="B25" t="n">
-        <v>89388</v>
+        <v>78503</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3409,25 +3444,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3438,10 +3473,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>557494.3515170069</v>
+        <v>557469.5464570362</v>
       </c>
       <c r="R25" t="n">
-        <v>7313522.549664274</v>
+        <v>7313597.186250712</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3510,10 +3545,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>95133831</v>
+        <v>95133000</v>
       </c>
       <c r="B26" t="n">
-        <v>56395</v>
+        <v>78437</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3526,37 +3561,35 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>2080</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skorpgelélav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rostania occultata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557561.2011936309</v>
+        <v>557469.5464570362</v>
       </c>
       <c r="R26" t="n">
-        <v>7313613.325183534</v>
+        <v>7313597.186250712</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3599,11 +3632,6 @@
       <c r="AB26" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3630,10 +3658,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>95133764</v>
+        <v>95133592</v>
       </c>
       <c r="B27" t="n">
-        <v>89317</v>
+        <v>89388</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3646,21 +3674,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3242</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3671,10 +3699,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557565.6280339119</v>
+        <v>557494.3515170069</v>
       </c>
       <c r="R27" t="n">
-        <v>7313576.255149641</v>
+        <v>7313522.549664274</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3743,10 +3771,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>95133725</v>
+        <v>95133831</v>
       </c>
       <c r="B28" t="n">
-        <v>73698</v>
+        <v>56395</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3759,35 +3787,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1467</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>557541.3539947418</v>
+        <v>557561.2011936309</v>
       </c>
       <c r="R28" t="n">
-        <v>7313523.088473954</v>
+        <v>7313613.325183534</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3830,6 +3860,11 @@
       <c r="AB28" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3856,10 +3891,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>95181707</v>
+        <v>95133764</v>
       </c>
       <c r="B29" t="n">
-        <v>89410</v>
+        <v>89317</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3872,21 +3907,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>3242</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3897,10 +3932,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>557628.5280401763</v>
+        <v>557565.6280339119</v>
       </c>
       <c r="R29" t="n">
-        <v>7313660.009347937</v>
+        <v>7313576.255149641</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3957,22 +3992,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>95181737</v>
+        <v>95133725</v>
       </c>
       <c r="B30" t="n">
-        <v>89742</v>
+        <v>73698</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3981,25 +4016,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1506</v>
+        <v>1467</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4010,10 +4045,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>557652.6369780133</v>
+        <v>557541.3539947418</v>
       </c>
       <c r="R30" t="n">
-        <v>7313660.496240489</v>
+        <v>7313523.088473954</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4070,22 +4105,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>98386022</v>
+        <v>95181707</v>
       </c>
       <c r="B31" t="n">
-        <v>56540</v>
+        <v>89410</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4098,44 +4133,38 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>557499.7120975225</v>
+        <v>557628.5280401763</v>
       </c>
       <c r="R31" t="n">
-        <v>7313662.311308526</v>
+        <v>7313660.009347937</v>
       </c>
       <c r="S31" t="n">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4159,7 +4188,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-01-17</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
@@ -4169,7 +4198,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-01-17</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -4201,10 +4230,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>105524543</v>
+        <v>95181737</v>
       </c>
       <c r="B32" t="n">
-        <v>56395</v>
+        <v>89742</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4213,49 +4242,42 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1506</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ribbo, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>557722.2764535763</v>
+        <v>557652.6369780133</v>
       </c>
       <c r="R32" t="n">
-        <v>7313451.194894779</v>
+        <v>7313660.496240489</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4279,7 +4301,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-01-02</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
@@ -4289,7 +4311,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-01-02</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -4321,10 +4343,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>105524498</v>
+        <v>98386022</v>
       </c>
       <c r="B33" t="n">
-        <v>56395</v>
+        <v>56540</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4337,45 +4359,44 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Ribbo, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>557627.1049988176</v>
+        <v>557499.7120975225</v>
       </c>
       <c r="R33" t="n">
-        <v>7313224.253787322</v>
+        <v>7313662.311308526</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>98</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4399,7 +4420,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-01-02</t>
+          <t>2022-01-17</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
@@ -4409,7 +4430,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-01-02</t>
+          <t>2022-01-17</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -4441,7 +4462,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>105524457</v>
+        <v>105524543</v>
       </c>
       <c r="B34" t="n">
         <v>56395</v>
@@ -4489,10 +4510,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>557498.2867395905</v>
+        <v>557722.2764535763</v>
       </c>
       <c r="R34" t="n">
-        <v>7313286.590600722</v>
+        <v>7313451.194894779</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4561,10 +4582,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>105524805</v>
+        <v>105524498</v>
       </c>
       <c r="B35" t="n">
-        <v>78569</v>
+        <v>56395</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4577,26 +4598,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4604,10 +4630,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>557707.6931877108</v>
+        <v>557627.1049988176</v>
       </c>
       <c r="R35" t="n">
-        <v>7313505.212126551</v>
+        <v>7313224.253787322</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4652,18 +4678,12 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På rönn</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4679,6 +4699,247 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>105524457</v>
+      </c>
+      <c r="B36" t="n">
+        <v>56395</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Ribbo, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>557498.2867395905</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7313286.590600722</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2023-01-02</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2023-01-02</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>105524805</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78569</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Ribbo, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>557707.6931877108</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7313505.212126551</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2023-01-02</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2023-01-02</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På rönn</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24409-2021 artfynd.xlsx
+++ b/artfynd/A 24409-2021 artfynd.xlsx
@@ -1293,10 +1293,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120486082</v>
+        <v>120486185</v>
       </c>
       <c r="B7" t="n">
-        <v>56532</v>
+        <v>56524</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1305,25 +1305,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1394,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>vid  sista  på kartan markerade huset före sjöforsen,   mellan Ammarnäsvgn och Gautsträsk</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1421,10 +1426,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120486185</v>
+        <v>120486082</v>
       </c>
       <c r="B8" t="n">
-        <v>56524</v>
+        <v>56532</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1433,25 +1438,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1512,7 +1517,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1522,12 +1527,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>vid  sista  på kartan markerade huset före sjöforsen,   mellan Ammarnäsvgn och Gautsträsk</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 24409-2021 artfynd.xlsx
+++ b/artfynd/A 24409-2021 artfynd.xlsx
@@ -1293,10 +1293,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120486185</v>
+        <v>120486082</v>
       </c>
       <c r="B7" t="n">
-        <v>56524</v>
+        <v>56532</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1305,25 +1305,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,12 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>vid  sista  på kartan markerade huset före sjöforsen,   mellan Ammarnäsvgn och Gautsträsk</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1426,10 +1421,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120486082</v>
+        <v>120486185</v>
       </c>
       <c r="B8" t="n">
-        <v>56532</v>
+        <v>56524</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1438,25 +1433,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1517,7 +1512,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1527,7 +1522,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>vid  sista  på kartan markerade huset före sjöforsen,   mellan Ammarnäsvgn och Gautsträsk</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 24409-2021 artfynd.xlsx
+++ b/artfynd/A 24409-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1169,10 +1169,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111702865</v>
+        <v>120486185</v>
       </c>
       <c r="B6" t="n">
-        <v>56543</v>
+        <v>56551</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,30 +1185,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -1251,22 +1255,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>vid  sista  på kartan markerade huset före sjöforsen,   mellan Ammarnäsvgn och Gautsträsk</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1281,22 +1290,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erik Owusu-Ansah</t>
+          <t>Bernt-Erik Nordenström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erik Owusu-Ansah</t>
+          <t>Bernt-Erik Nordenström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120486185</v>
+        <v>120486082</v>
       </c>
       <c r="B7" t="n">
-        <v>56551</v>
+        <v>56559</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1305,25 +1314,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1384,7 +1393,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,12 +1403,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>vid  sista  på kartan markerade huset före sjöforsen,   mellan Ammarnäsvgn och Gautsträsk</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1426,10 +1430,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120486082</v>
+        <v>66544522</v>
       </c>
       <c r="B8" t="n">
-        <v>56559</v>
+        <v>89412</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1438,57 +1442,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Börtingtjärnen, Nabbnäs, Ly lm</t>
+          <t>Nabbnäs E, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557511</v>
+        <v>557343.9500621258</v>
       </c>
       <c r="R8" t="n">
-        <v>7314093</v>
+        <v>7313805.357225817</v>
       </c>
       <c r="S8" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1512,22 +1500,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1538,26 +1526,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>25250</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bernt-Erik Nordenström</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bernt-Erik Nordenström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>66544522</v>
+        <v>66544521</v>
       </c>
       <c r="B9" t="n">
-        <v>89412</v>
+        <v>77177</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1570,21 +1563,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1594,10 +1587,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557343.9500621258</v>
+        <v>557552.5743103321</v>
       </c>
       <c r="R9" t="n">
-        <v>7313805.357225817</v>
+        <v>7313818.131272775</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1653,7 +1646,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>25250</t>
+          <t>25249</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1671,10 +1664,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>66544521</v>
+        <v>66544520</v>
       </c>
       <c r="B10" t="n">
-        <v>77177</v>
+        <v>89317</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1687,21 +1680,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>3242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1711,10 +1704,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557552.5743103321</v>
+        <v>557585.4108167831</v>
       </c>
       <c r="R10" t="n">
-        <v>7313818.131272775</v>
+        <v>7313811.444012655</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1770,7 +1763,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>25249</t>
+          <t>25248</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1788,10 +1781,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>66544520</v>
+        <v>93819789</v>
       </c>
       <c r="B11" t="n">
-        <v>89317</v>
+        <v>57193</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1804,37 +1797,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3242</v>
+        <v>206004</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nabbnäs E, Ly lm</t>
+          <t>Gautsträsk, Ammarnäs, Ammarnäs, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557585.4108167831</v>
+        <v>557932.0448319349</v>
       </c>
       <c r="R11" t="n">
-        <v>7313811.444012655</v>
+        <v>7313851.940869053</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1858,7 +1859,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2021-05-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1868,7 +1869,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2021-05-21</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1884,31 +1885,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>25248</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Rolf Segerstedt</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Rolf Segerstedt</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>93819789</v>
+        <v>95181786</v>
       </c>
       <c r="B12" t="n">
-        <v>57193</v>
+        <v>89317</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1921,42 +1917,35 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>206004</v>
+        <v>3242</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gautsträsk, Ammarnäs, Ammarnäs, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557932.0448319349</v>
+        <v>557659.3462767266</v>
       </c>
       <c r="R12" t="n">
-        <v>7313851.940869053</v>
+        <v>7313753.322394</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1983,7 +1972,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-05-21</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -1993,7 +1982,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-05-21</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -2013,22 +2002,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Rolf Segerstedt</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Rolf Segerstedt</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>95181786</v>
+        <v>106068564</v>
       </c>
       <c r="B13" t="n">
-        <v>89317</v>
+        <v>56395</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2041,38 +2030,45 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3242</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Nabbnäs, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557659.3462767266</v>
+        <v>557341.094957336</v>
       </c>
       <c r="R13" t="n">
-        <v>7313753.322394</v>
+        <v>7314415.254025667</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2096,7 +2092,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2023-01-04</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -2106,7 +2102,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2023-01-04</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2138,10 +2134,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>106068564</v>
+        <v>106068609</v>
       </c>
       <c r="B14" t="n">
-        <v>56395</v>
+        <v>56540</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2154,31 +2150,35 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2186,10 +2186,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557341.094957336</v>
+        <v>557178.5243778926</v>
       </c>
       <c r="R14" t="n">
-        <v>7314415.254025667</v>
+        <v>7314676.100958445</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>106068609</v>
+        <v>106181512</v>
       </c>
       <c r="B15" t="n">
-        <v>56540</v>
+        <v>56395</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2274,46 +2274,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nabbnäs, Ly lm</t>
+          <t>Börtingtjärn, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557178.5243778926</v>
+        <v>557563.1252945462</v>
       </c>
       <c r="R15" t="n">
-        <v>7314676.100958445</v>
+        <v>7313923.278383149</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2340,7 +2336,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-01-04</t>
+          <t>2023-01-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -2350,12 +2346,17 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-01-04</t>
+          <t>2023-01-24</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rinhack. Tämligen färskt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2382,7 +2383,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>106181512</v>
+        <v>106181822</v>
       </c>
       <c r="B16" t="n">
         <v>56395</v>
@@ -2426,17 +2427,17 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Börtingtjärn, Ly lm</t>
+          <t>Börtingtjärn, Nabbnäs, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>557563.1252945462</v>
+        <v>557150.1442167946</v>
       </c>
       <c r="R16" t="n">
-        <v>7313923.278383149</v>
+        <v>7314562.870367996</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2476,11 +2477,6 @@
       <c r="AB16" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rinhack. Tämligen färskt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2507,10 +2503,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>106181822</v>
+        <v>66544516</v>
       </c>
       <c r="B17" t="n">
-        <v>56395</v>
+        <v>78570</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2523,45 +2519,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Börtingtjärn, Nabbnäs, Ly lm</t>
+          <t>Nabbnäs E, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>557150.1442167946</v>
+        <v>557811.1036065554</v>
       </c>
       <c r="R17" t="n">
-        <v>7314562.870367996</v>
+        <v>7313445.641976926</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2585,7 +2573,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-01-24</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -2595,7 +2583,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-01-24</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2611,26 +2599,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>25244</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>66544516</v>
+        <v>66544518</v>
       </c>
       <c r="B18" t="n">
-        <v>78570</v>
+        <v>78602</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2639,25 +2632,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2726,7 +2719,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>25244</t>
+          <t>25246</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2744,10 +2737,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>66544518</v>
+        <v>66544517</v>
       </c>
       <c r="B19" t="n">
-        <v>78602</v>
+        <v>78503</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2760,21 +2753,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2843,7 +2836,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>25246</t>
+          <t>25245</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2861,10 +2854,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>66544517</v>
+        <v>95133646</v>
       </c>
       <c r="B20" t="n">
-        <v>78503</v>
+        <v>56411</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2873,41 +2866,44 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nabbnäs E, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>557811.1036065554</v>
+        <v>557549.2252521986</v>
       </c>
       <c r="R20" t="n">
-        <v>7313445.641976926</v>
+        <v>7313517.938556333</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2931,7 +2927,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -2941,7 +2937,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -2957,31 +2953,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>25245</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>95133646</v>
+        <v>95133123</v>
       </c>
       <c r="B21" t="n">
-        <v>56411</v>
+        <v>78072</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2994,37 +2985,35 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>557549.2252521986</v>
+        <v>557451.3615532392</v>
       </c>
       <c r="R21" t="n">
-        <v>7313517.938556333</v>
+        <v>7313525.767571403</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3093,10 +3082,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>95133123</v>
+        <v>95133125</v>
       </c>
       <c r="B22" t="n">
-        <v>78072</v>
+        <v>78098</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3109,21 +3098,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3206,10 +3195,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>95133125</v>
+        <v>95133810</v>
       </c>
       <c r="B23" t="n">
-        <v>78098</v>
+        <v>89317</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3222,21 +3211,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>3242</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3247,10 +3236,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>557451.3615532392</v>
+        <v>557561.2011936309</v>
       </c>
       <c r="R23" t="n">
-        <v>7313525.767571403</v>
+        <v>7313613.325183534</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3319,10 +3308,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>95133810</v>
+        <v>95132995</v>
       </c>
       <c r="B24" t="n">
-        <v>89317</v>
+        <v>78503</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3331,25 +3320,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3242</v>
+        <v>6456</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3360,10 +3349,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>557561.2011936309</v>
+        <v>557469.5464570362</v>
       </c>
       <c r="R24" t="n">
-        <v>7313613.325183534</v>
+        <v>7313597.186250712</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3432,10 +3421,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>95132995</v>
+        <v>95133000</v>
       </c>
       <c r="B25" t="n">
-        <v>78503</v>
+        <v>78437</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3444,25 +3433,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>2080</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skorpgelélav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Rostania occultata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3545,10 +3534,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>95133000</v>
+        <v>95133592</v>
       </c>
       <c r="B26" t="n">
-        <v>78437</v>
+        <v>89388</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3561,21 +3550,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2080</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skorpgelélav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rostania occultata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3586,10 +3575,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557469.5464570362</v>
+        <v>557494.3515170069</v>
       </c>
       <c r="R26" t="n">
-        <v>7313597.186250712</v>
+        <v>7313522.549664274</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3658,10 +3647,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>95133592</v>
+        <v>95133831</v>
       </c>
       <c r="B27" t="n">
-        <v>89388</v>
+        <v>56395</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3674,35 +3663,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557494.3515170069</v>
+        <v>557561.2011936309</v>
       </c>
       <c r="R27" t="n">
-        <v>7313522.549664274</v>
+        <v>7313613.325183534</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3745,6 +3736,11 @@
       <c r="AB27" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3771,10 +3767,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>95133831</v>
+        <v>95133764</v>
       </c>
       <c r="B28" t="n">
-        <v>56395</v>
+        <v>89317</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3787,37 +3783,35 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>3242</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>557561.2011936309</v>
+        <v>557565.6280339119</v>
       </c>
       <c r="R28" t="n">
-        <v>7313613.325183534</v>
+        <v>7313576.255149641</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3860,11 +3854,6 @@
       <c r="AB28" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3891,10 +3880,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>95133764</v>
+        <v>95133725</v>
       </c>
       <c r="B29" t="n">
-        <v>89317</v>
+        <v>73698</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3907,21 +3896,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3242</v>
+        <v>1467</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3932,10 +3921,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>557565.6280339119</v>
+        <v>557541.3539947418</v>
       </c>
       <c r="R29" t="n">
-        <v>7313576.255149641</v>
+        <v>7313523.088473954</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -4004,10 +3993,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>95133725</v>
+        <v>95181707</v>
       </c>
       <c r="B30" t="n">
-        <v>73698</v>
+        <v>89410</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4020,21 +4009,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4045,10 +4034,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>557541.3539947418</v>
+        <v>557628.5280401763</v>
       </c>
       <c r="R30" t="n">
-        <v>7313523.088473954</v>
+        <v>7313660.009347937</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4105,22 +4094,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>95181707</v>
+        <v>95181737</v>
       </c>
       <c r="B31" t="n">
-        <v>89410</v>
+        <v>89742</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4129,25 +4118,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>1506</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4158,10 +4147,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>557628.5280401763</v>
+        <v>557652.6369780133</v>
       </c>
       <c r="R31" t="n">
-        <v>7313660.009347937</v>
+        <v>7313660.496240489</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4230,10 +4219,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>95181737</v>
+        <v>98386022</v>
       </c>
       <c r="B32" t="n">
-        <v>89742</v>
+        <v>56540</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4242,42 +4231,48 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1506</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>557652.6369780133</v>
+        <v>557499.7120975225</v>
       </c>
       <c r="R32" t="n">
-        <v>7313660.496240489</v>
+        <v>7313662.311308526</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4301,7 +4296,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2022-01-17</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
@@ -4311,7 +4306,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2022-01-17</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -4343,10 +4338,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>98386022</v>
+        <v>105524543</v>
       </c>
       <c r="B33" t="n">
-        <v>56540</v>
+        <v>56395</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4359,44 +4354,45 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Ribbo, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>557499.7120975225</v>
+        <v>557722.2764535763</v>
       </c>
       <c r="R33" t="n">
-        <v>7313662.311308526</v>
+        <v>7313451.194894779</v>
       </c>
       <c r="S33" t="n">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4420,7 +4416,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2022-01-17</t>
+          <t>2023-01-02</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
@@ -4430,7 +4426,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2022-01-17</t>
+          <t>2023-01-02</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -4462,7 +4458,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>105524543</v>
+        <v>105524498</v>
       </c>
       <c r="B34" t="n">
         <v>56395</v>
@@ -4500,7 +4496,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4510,10 +4506,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>557722.2764535763</v>
+        <v>557627.1049988176</v>
       </c>
       <c r="R34" t="n">
-        <v>7313451.194894779</v>
+        <v>7313224.253787322</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4582,7 +4578,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>105524498</v>
+        <v>105524457</v>
       </c>
       <c r="B35" t="n">
         <v>56395</v>
@@ -4620,7 +4616,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4630,10 +4626,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>557627.1049988176</v>
+        <v>557498.2867395905</v>
       </c>
       <c r="R35" t="n">
-        <v>7313224.253787322</v>
+        <v>7313286.590600722</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4702,10 +4698,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>105524457</v>
+        <v>105524805</v>
       </c>
       <c r="B36" t="n">
-        <v>56395</v>
+        <v>78569</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4718,31 +4714,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4750,10 +4741,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557498.2867395905</v>
+        <v>557707.6931877108</v>
       </c>
       <c r="R36" t="n">
-        <v>7313286.590600722</v>
+        <v>7313505.212126551</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4798,12 +4789,18 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På rönn</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4819,127 +4816,6 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>105524805</v>
-      </c>
-      <c r="B37" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Ribbo, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>557707.6931877108</v>
-      </c>
-      <c r="R37" t="n">
-        <v>7313505.212126551</v>
-      </c>
-      <c r="S37" t="n">
-        <v>10</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2023-01-02</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2023-01-02</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På rönn</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="inlineStr"/>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24409-2021 artfynd.xlsx
+++ b/artfynd/A 24409-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>46095039</v>
+        <v>66544522</v>
       </c>
       <c r="B2" t="n">
-        <v>56806</v>
+        <v>89412</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103001</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Börtingtjärnen, Nabbnäs, Ly lm</t>
+          <t>Nabbnäs E, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557511.0569535147</v>
+        <v>557343.9500621258</v>
       </c>
       <c r="R2" t="n">
-        <v>7314093.299974133</v>
+        <v>7313805.357225817</v>
       </c>
       <c r="S2" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-05-29</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>04:16</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-05-29</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>04:23</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,26 +771,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>25250</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bernt-Erik Nordenström</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bernt-Erik Nordenström, Erik Nordenström, Jonas Nordenström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>52186368</v>
+        <v>66544521</v>
       </c>
       <c r="B3" t="n">
-        <v>56540</v>
+        <v>77177</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,46 +808,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Börtingtjärnen, Nabbnäs, Ly lm</t>
+          <t>Nabbnäs E, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557511.0569535147</v>
+        <v>557552.5743103321</v>
       </c>
       <c r="R3" t="n">
-        <v>7314093.299974133</v>
+        <v>7313818.131272775</v>
       </c>
       <c r="S3" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,22 +862,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-02-04</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-02-04</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,26 +888,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>25249</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bernt-Erik Nordenström</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bernt-Erik Nordenström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>93615239</v>
+        <v>66544520</v>
       </c>
       <c r="B4" t="n">
-        <v>56812</v>
+        <v>89317</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,49 +925,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102999</v>
+        <v>3242</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Börtingtjärnen, Nabbnäs, Ly lm</t>
+          <t>Nabbnäs E, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>557511.0569535147</v>
+        <v>557585.4108167831</v>
       </c>
       <c r="R4" t="n">
-        <v>7314093.299974133</v>
+        <v>7313811.444012655</v>
       </c>
       <c r="S4" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,22 +979,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-05-20</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-05-20</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,26 +1005,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>25248</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bernt-Erik Nordenström</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bernt-Erik Nordenström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>86238581</v>
+        <v>93819789</v>
       </c>
       <c r="B5" t="n">
-        <v>55504</v>
+        <v>57193</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,57 +1038,49 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102931</v>
+        <v>206004</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bläsand</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Mareca penelope</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Börtingtjärnen, Nabbnäs, Ly lm</t>
+          <t>Gautsträsk, Ammarnäs, Ammarnäs, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557511.0569535147</v>
+        <v>557932.0448319349</v>
       </c>
       <c r="R5" t="n">
-        <v>7314093.299974133</v>
+        <v>7313851.940869053</v>
       </c>
       <c r="S5" t="n">
-        <v>127</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1127,7 +1104,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-06-07</t>
+          <t>2021-05-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1137,7 +1114,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-06-07</t>
+          <t>2021-05-21</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1157,22 +1134,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Petter Nordvander</t>
+          <t>Rolf Segerstedt</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Petter Nordvander</t>
+          <t>Rolf Segerstedt</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120486185</v>
+        <v>95181786</v>
       </c>
       <c r="B6" t="n">
-        <v>56551</v>
+        <v>89317</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,53 +1162,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>3242</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Börtingtjärnen, Nabbnäs, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557511</v>
+        <v>557659.3462767266</v>
       </c>
       <c r="R6" t="n">
-        <v>7314093</v>
+        <v>7313753.322394</v>
       </c>
       <c r="S6" t="n">
-        <v>127</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1255,27 +1217,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>vid  sista  på kartan markerade huset före sjöforsen,   mellan Ammarnäsvgn och Gautsträsk</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,22 +1247,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bernt-Erik Nordenström</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bernt-Erik Nordenström</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120486082</v>
+        <v>66544516</v>
       </c>
       <c r="B7" t="n">
-        <v>56559</v>
+        <v>78570</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1314,57 +1271,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Börtingtjärnen, Nabbnäs, Ly lm</t>
+          <t>Nabbnäs E, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557511</v>
+        <v>557811.1036065554</v>
       </c>
       <c r="R7" t="n">
-        <v>7314093</v>
+        <v>7313445.641976926</v>
       </c>
       <c r="S7" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1388,22 +1329,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1414,26 +1355,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>25244</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bernt-Erik Nordenström</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bernt-Erik Nordenström</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>66544522</v>
+        <v>66544518</v>
       </c>
       <c r="B8" t="n">
-        <v>89412</v>
+        <v>78602</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1442,25 +1388,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1470,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557343.9500621258</v>
+        <v>557811.1036065554</v>
       </c>
       <c r="R8" t="n">
-        <v>7313805.357225817</v>
+        <v>7313445.641976926</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1529,7 +1475,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>25250</t>
+          <t>25246</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1540,17 +1486,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>66544521</v>
+        <v>66544517</v>
       </c>
       <c r="B9" t="n">
-        <v>77177</v>
+        <v>78503</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1559,25 +1505,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1587,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557552.5743103321</v>
+        <v>557811.1036065554</v>
       </c>
       <c r="R9" t="n">
-        <v>7313818.131272775</v>
+        <v>7313445.641976926</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1646,7 +1592,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>25249</t>
+          <t>25245</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1657,17 +1603,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>66544520</v>
+        <v>95133646</v>
       </c>
       <c r="B10" t="n">
-        <v>89317</v>
+        <v>56411</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1680,37 +1626,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3242</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nabbnäs E, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557585.4108167831</v>
+        <v>557549.2252521986</v>
       </c>
       <c r="R10" t="n">
-        <v>7313811.444012655</v>
+        <v>7313517.938556333</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1734,7 +1683,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1744,7 +1693,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1760,31 +1709,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>25248</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>93819789</v>
+        <v>95133123</v>
       </c>
       <c r="B11" t="n">
-        <v>57193</v>
+        <v>78072</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1797,42 +1741,35 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>206004</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gautsträsk, Ammarnäs, Ammarnäs, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557932.0448319349</v>
+        <v>557451.3615532392</v>
       </c>
       <c r="R11" t="n">
-        <v>7313851.940869053</v>
+        <v>7313525.767571403</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1859,7 +1796,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-05-21</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1869,7 +1806,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-05-21</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1889,22 +1826,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Rolf Segerstedt</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Rolf Segerstedt</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>95181786</v>
+        <v>95133125</v>
       </c>
       <c r="B12" t="n">
-        <v>89317</v>
+        <v>78098</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1917,21 +1854,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3242</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1942,10 +1879,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557659.3462767266</v>
+        <v>557451.3615532392</v>
       </c>
       <c r="R12" t="n">
-        <v>7313753.322394</v>
+        <v>7313525.767571403</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2002,22 +1939,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>106068564</v>
+        <v>95133810</v>
       </c>
       <c r="B13" t="n">
-        <v>56395</v>
+        <v>89317</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2030,45 +1967,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>3242</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nabbnäs, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557341.094957336</v>
+        <v>557561.2011936309</v>
       </c>
       <c r="R13" t="n">
-        <v>7314415.254025667</v>
+        <v>7313613.325183534</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2092,7 +2022,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-01-04</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -2102,7 +2032,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-01-04</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2122,22 +2052,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>106068609</v>
+        <v>95132995</v>
       </c>
       <c r="B14" t="n">
-        <v>56540</v>
+        <v>78503</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2146,53 +2076,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nabbnäs, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557178.5243778926</v>
+        <v>557469.5464570362</v>
       </c>
       <c r="R14" t="n">
-        <v>7314676.100958445</v>
+        <v>7313597.186250712</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2216,7 +2135,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-01-04</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2226,7 +2145,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-01-04</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2246,22 +2165,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>106181512</v>
+        <v>95133000</v>
       </c>
       <c r="B15" t="n">
-        <v>56395</v>
+        <v>78437</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2274,45 +2193,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>2080</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skorpgelélav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rostania occultata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Börtingtjärn, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557563.1252945462</v>
+        <v>557469.5464570362</v>
       </c>
       <c r="R15" t="n">
-        <v>7313923.278383149</v>
+        <v>7313597.186250712</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2336,7 +2248,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-01-24</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -2346,17 +2258,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-01-24</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rinhack. Tämligen färskt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2371,22 +2278,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>106181822</v>
+        <v>95133592</v>
       </c>
       <c r="B16" t="n">
-        <v>56395</v>
+        <v>89388</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2399,42 +2306,35 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Börtingtjärn, Nabbnäs, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>557150.1442167946</v>
+        <v>557494.3515170069</v>
       </c>
       <c r="R16" t="n">
-        <v>7314562.870367996</v>
+        <v>7313522.549664274</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2461,7 +2361,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-01-24</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -2471,7 +2371,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-01-24</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2491,22 +2391,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>66544516</v>
+        <v>95133831</v>
       </c>
       <c r="B17" t="n">
-        <v>78570</v>
+        <v>56395</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2519,37 +2419,40 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nabbnäs E, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>557811.1036065554</v>
+        <v>557561.2011936309</v>
       </c>
       <c r="R17" t="n">
-        <v>7313445.641976926</v>
+        <v>7313613.325183534</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2573,7 +2476,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -2583,7 +2486,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2591,6 +2494,11 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2599,31 +2507,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>25244</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>66544518</v>
+        <v>95133764</v>
       </c>
       <c r="B18" t="n">
-        <v>78602</v>
+        <v>89317</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2632,41 +2535,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>3242</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nabbnäs E, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>557811.1036065554</v>
+        <v>557565.6280339119</v>
       </c>
       <c r="R18" t="n">
-        <v>7313445.641976926</v>
+        <v>7313576.255149641</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2690,7 +2594,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2700,7 +2604,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2716,31 +2620,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>25246</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>66544517</v>
+        <v>95133725</v>
       </c>
       <c r="B19" t="n">
-        <v>78503</v>
+        <v>73698</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2749,41 +2648,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6456</v>
+        <v>1467</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nabbnäs E, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>557811.1036065554</v>
+        <v>557541.3539947418</v>
       </c>
       <c r="R19" t="n">
-        <v>7313445.641976926</v>
+        <v>7313523.088473954</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2807,7 +2707,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -2817,7 +2717,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
+          <t>2021-07-28</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -2833,31 +2733,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>25245</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>95133646</v>
+        <v>95181707</v>
       </c>
       <c r="B20" t="n">
-        <v>56411</v>
+        <v>89410</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2870,37 +2765,35 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>557549.2252521986</v>
+        <v>557628.5280401763</v>
       </c>
       <c r="R20" t="n">
-        <v>7313517.938556333</v>
+        <v>7313660.009347937</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2957,22 +2850,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>95133123</v>
+        <v>95181737</v>
       </c>
       <c r="B21" t="n">
-        <v>78072</v>
+        <v>89742</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2981,25 +2874,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>1506</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3010,10 +2903,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>557451.3615532392</v>
+        <v>557652.6369780133</v>
       </c>
       <c r="R21" t="n">
-        <v>7313525.767571403</v>
+        <v>7313660.496240489</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3070,22 +2963,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>95133125</v>
+        <v>98386022</v>
       </c>
       <c r="B22" t="n">
-        <v>78098</v>
+        <v>56540</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3098,38 +2991,44 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>557451.3615532392</v>
+        <v>557499.7120975225</v>
       </c>
       <c r="R22" t="n">
-        <v>7313525.767571403</v>
+        <v>7313662.311308526</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3153,7 +3052,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2022-01-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -3163,7 +3062,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2022-01-17</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3183,22 +3082,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>95133810</v>
+        <v>105524543</v>
       </c>
       <c r="B23" t="n">
-        <v>89317</v>
+        <v>56395</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3211,38 +3110,45 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3242</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Ribbo, Ly lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>557561.2011936309</v>
+        <v>557722.2764535763</v>
       </c>
       <c r="R23" t="n">
-        <v>7313613.325183534</v>
+        <v>7313451.194894779</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3266,7 +3172,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2023-01-02</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -3276,7 +3182,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2023-01-02</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3296,22 +3202,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>95132995</v>
+        <v>105524805</v>
       </c>
       <c r="B24" t="n">
-        <v>78503</v>
+        <v>78569</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3320,42 +3226,44 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Ribbo, Ly lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>557469.5464570362</v>
+        <v>557707.6931877108</v>
       </c>
       <c r="R24" t="n">
-        <v>7313597.186250712</v>
+        <v>7313505.212126551</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3379,7 +3287,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2023-01-02</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -3389,7 +3297,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2023-01-02</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3397,1425 +3305,33 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På rönn</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>95133000</v>
-      </c>
-      <c r="B25" t="n">
-        <v>78437</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>2080</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Skorpgelélav</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Rostania occultata</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Sorsele, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>557469.5464570362</v>
-      </c>
-      <c r="R25" t="n">
-        <v>7313597.186250712</v>
-      </c>
-      <c r="S25" t="n">
-        <v>25</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2021-07-28</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2021-07-28</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>95133592</v>
-      </c>
-      <c r="B26" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Sorsele, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>557494.3515170069</v>
-      </c>
-      <c r="R26" t="n">
-        <v>7313522.549664274</v>
-      </c>
-      <c r="S26" t="n">
-        <v>25</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2021-07-28</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2021-07-28</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>95133831</v>
-      </c>
-      <c r="B27" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Sorsele, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>557561.2011936309</v>
-      </c>
-      <c r="R27" t="n">
-        <v>7313613.325183534</v>
-      </c>
-      <c r="S27" t="n">
-        <v>25</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2021-07-28</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2021-07-28</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>95133764</v>
-      </c>
-      <c r="B28" t="n">
-        <v>89317</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>3242</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Vitplätt</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Chaetodermella luna</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Sorsele, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>557565.6280339119</v>
-      </c>
-      <c r="R28" t="n">
-        <v>7313576.255149641</v>
-      </c>
-      <c r="S28" t="n">
-        <v>25</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2021-07-28</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2021-07-28</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>95133725</v>
-      </c>
-      <c r="B29" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>1467</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Rödbrun blekspik</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Sclerophora coniophaea</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Sorsele, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
-        <v>557541.3539947418</v>
-      </c>
-      <c r="R29" t="n">
-        <v>7313523.088473954</v>
-      </c>
-      <c r="S29" t="n">
-        <v>25</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2021-07-28</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2021-07-28</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>95181707</v>
-      </c>
-      <c r="B30" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Sorsele, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>557628.5280401763</v>
-      </c>
-      <c r="R30" t="n">
-        <v>7313660.009347937</v>
-      </c>
-      <c r="S30" t="n">
-        <v>25</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2021-07-28</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2021-07-28</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>95181737</v>
-      </c>
-      <c r="B31" t="n">
-        <v>89742</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>1506</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Ostticka</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Skeletocutis odora</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Sacc.) Ginns</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Sorsele, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>557652.6369780133</v>
-      </c>
-      <c r="R31" t="n">
-        <v>7313660.496240489</v>
-      </c>
-      <c r="S31" t="n">
-        <v>25</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2021-07-28</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2021-07-28</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>98386022</v>
-      </c>
-      <c r="B32" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Sorsele, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>557499.7120975225</v>
-      </c>
-      <c r="R32" t="n">
-        <v>7313662.311308526</v>
-      </c>
-      <c r="S32" t="n">
-        <v>98</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2022-01-17</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2022-01-17</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>105524543</v>
-      </c>
-      <c r="B33" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Ribbo, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>557722.2764535763</v>
-      </c>
-      <c r="R33" t="n">
-        <v>7313451.194894779</v>
-      </c>
-      <c r="S33" t="n">
-        <v>10</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2023-01-02</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2023-01-02</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>105524498</v>
-      </c>
-      <c r="B34" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Ribbo, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>557627.1049988176</v>
-      </c>
-      <c r="R34" t="n">
-        <v>7313224.253787322</v>
-      </c>
-      <c r="S34" t="n">
-        <v>10</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2023-01-02</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2023-01-02</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>105524457</v>
-      </c>
-      <c r="B35" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Ribbo, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>557498.2867395905</v>
-      </c>
-      <c r="R35" t="n">
-        <v>7313286.590600722</v>
-      </c>
-      <c r="S35" t="n">
-        <v>10</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2023-01-02</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2023-01-02</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>105524805</v>
-      </c>
-      <c r="B36" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Ribbo, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>557707.6931877108</v>
-      </c>
-      <c r="R36" t="n">
-        <v>7313505.212126551</v>
-      </c>
-      <c r="S36" t="n">
-        <v>10</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2023-01-02</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2023-01-02</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På rönn</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
